--- a/freshdesk_reply_log.xlsx
+++ b/freshdesk_reply_log.xlsx
@@ -446,17 +446,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng J_331582.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng J_331582.pdf</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -468,17 +468,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng E_766919.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng E_766919.pdf</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng K_578652.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng K_578652.pdf</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -512,17 +512,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng U_152114.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng U_152114.pdf</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -534,17 +534,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng F_262436.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng F_262436.pdf</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -556,17 +556,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng W_475239.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng W_475239.pdf</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -578,17 +578,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng T_479878.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng T_479878.pdf</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -600,17 +600,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng Z_473292.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng Z_473292.pdf</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng D_371439.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng D_371439.pdf</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -644,17 +644,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng M_261093.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng M_261093.pdf</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -666,17 +666,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng R_188383.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng R_188383.pdf</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -688,17 +688,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng A_626941.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng A_626941.pdf</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -710,17 +710,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng S_523289.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng S_523289.pdf</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -732,17 +732,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng F_882358.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng F_882358.pdf</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -754,17 +754,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng J_087704.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng J_087704.pdf</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng M_378525.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng M_378525.pdf</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -798,17 +798,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng C_483639.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng C_483639.pdf</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -820,17 +820,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng M_808763.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng M_808763.pdf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -842,17 +842,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng L_219134.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng L_219134.pdf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -864,17 +864,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng P_217423.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng P_217423.pdf</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -886,17 +886,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng I_027741.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng I_027741.pdf</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -908,17 +908,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng E_822937.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng E_822937.pdf</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng H_665631.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng H_665631.pdf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng H_460396.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng H_460396.pdf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -974,17 +974,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng I_483415.docx</t>
+          <t>CHUNG TU Bank 3_ZALOPAY_Khách hàng I_483415.pdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng O_961894.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng O_961894.pdf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng E_216873.docx</t>
+          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng E_216873.pdf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1040,17 +1040,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CHUNG TU Bank 1_ZALOPAY_Khách hàng U_358759.docx</t>
+          <t>CHUNG TU Bank 2_ZALOPAY_Khách hàng U_358759.pdf</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SUCCESS (MOCK)</t>
+          <t>SKIPPED (bỏ chọn)</t>
         </is>
       </c>
     </row>

--- a/freshdesk_reply_log.xlsx
+++ b/freshdesk_reply_log.xlsx
@@ -451,12 +451,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -473,12 +473,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -517,12 +517,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -539,12 +539,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -561,12 +561,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -605,12 +605,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -627,12 +627,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -693,12 +693,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -737,12 +737,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -759,12 +759,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -781,12 +781,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -847,12 +847,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -869,12 +869,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -891,12 +891,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -913,12 +913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -935,12 +935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['bank_mock@mockbank.com', 'banksupport@vng.com.vn', 'chargebackzp@vng.com.vn']</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SKIPPED (bỏ chọn)</t>
+          <t>SUCCESS (MOCK)</t>
         </is>
       </c>
     </row>
